--- a/深燃/双活同步数据迁移概览021713.xlsx
+++ b/深燃/双活同步数据迁移概览021713.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\customer\深燃\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A822F7DC-1249-4746-A334-5CBE826DE436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0CFD4A-D385-4B18-9259-9ABC78F79F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
